--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536121_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536121_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. KROHNERT MOTO</t>
+          <t>D. GONZALEZ LONGARELA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -641,67 +641,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9424</v>
+        <v>5.9334</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8093</v>
+        <v>5.5971</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1331</v>
+        <v>0.3363</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4816</v>
+        <v>2.2347</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2779</v>
+        <v>0.229</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2037</v>
+        <v>2.0058</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9491</v>
+        <v>3.3172</v>
       </c>
       <c r="K3" t="n">
-        <v>0.078</v>
+        <v>0.6441</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8711</v>
+        <v>2.6731</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4675</v>
+        <v>-1.0825</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1999</v>
+        <v>-0.4152</v>
       </c>
       <c r="O3" t="n">
         <v>-0.6673</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.39</v>
+        <v>1.9499</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1448</v>
+        <v>-0.195</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7549</v>
+        <v>2.1448</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9677</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6178</v>
+        <v>0.6976</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3499</v>
+        <v>-0.1689</v>
       </c>
       <c r="V3" t="n">
-        <v>1.883</v>
+        <v>1.2201</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3872</v>
+        <v>1.7772</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5042</v>
+        <v>-0.5571</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>D. KROHNERT MOTO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -724,67 +724,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7193</v>
+        <v>3.9424</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1634</v>
+        <v>2.8093</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5559</v>
+        <v>1.1331</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.5806</v>
+        <v>1.4816</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4431</v>
+        <v>0.2779</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0237</v>
+        <v>1.2037</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2963</v>
+        <v>1.9491</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9272</v>
+        <v>0.078</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2235</v>
+        <v>1.8711</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2843</v>
+        <v>-0.4675</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4841</v>
+        <v>0.1999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8001</v>
+        <v>-0.6673</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9749</v>
+        <v>-0.39</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1699</v>
+        <v>-2.1448</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1448</v>
+        <v>1.7549</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1689</v>
+        <v>0.9677</v>
       </c>
       <c r="T4" t="n">
-        <v>0.911</v>
+        <v>0.6178</v>
       </c>
       <c r="U4" t="n">
-        <v>0.258</v>
+        <v>0.3499</v>
       </c>
       <c r="V4" t="n">
-        <v>3.156</v>
+        <v>1.883</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7187</v>
+        <v>2.3872</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4373</v>
+        <v>-0.5042</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. GONZALEZ LONGARELA</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -807,67 +807,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1957</v>
+        <v>3.7193</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8595</v>
+        <v>2.1634</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3363</v>
+        <v>1.5559</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5029</v>
+        <v>-1.5806</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0786</v>
+        <v>0.4431</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4243</v>
+        <v>-2.0237</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5796</v>
+        <v>-0.2963</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3366</v>
+        <v>0.9272</v>
       </c>
       <c r="L5" t="n">
-        <v>0.243</v>
+        <v>-1.2235</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.0825</v>
+        <v>-1.2843</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4152</v>
+        <v>-0.4841</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6673</v>
+        <v>-0.8001</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9499</v>
+        <v>0.9749</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.195</v>
+        <v>-1.1699</v>
       </c>
       <c r="R5" t="n">
         <v>2.1448</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5286999999999999</v>
+        <v>1.1689</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6976</v>
+        <v>0.911</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1689</v>
+        <v>0.258</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2201</v>
+        <v>3.156</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7772</v>
+        <v>2.7187</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5571</v>
+        <v>0.4373</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GONZALEZ  LONGARELA</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,67 +890,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7376</v>
+        <v>1.965</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7376</v>
+        <v>1.752</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.213</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7376</v>
+        <v>3.4934</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3075</v>
+        <v>2.6395</v>
       </c>
       <c r="I6" t="n">
-        <v>2.4301</v>
+        <v>0.8538</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7376</v>
+        <v>5.5239</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3075</v>
+        <v>3.6043</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4301</v>
+        <v>1.9196</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-2.0305</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.9648</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-1.0658</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-1.5599</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.0947</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.5348</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.3101</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.3757</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.0529</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2256</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,67 +973,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.965</v>
+        <v>0.2381</v>
       </c>
       <c r="E7" t="n">
-        <v>1.752</v>
+        <v>0.2679</v>
       </c>
       <c r="F7" t="n">
-        <v>0.213</v>
+        <v>-0.0298</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4934</v>
+        <v>-0.2484</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6395</v>
+        <v>0.1566</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8538</v>
+        <v>-0.405</v>
       </c>
       <c r="J7" t="n">
-        <v>5.5239</v>
+        <v>0.0205</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6043</v>
+        <v>0.0205</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9196</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0305</v>
+        <v>-0.2689</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9648</v>
+        <v>0.1361</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0658</v>
+        <v>-0.405</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5599</v>
+        <v>0.195</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.0947</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5348</v>
+        <v>0.195</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3101</v>
+        <v>0.2915</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3757</v>
+        <v>0.2473</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.0442</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2786</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0529</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2256</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>P. SUAREZ CUSTODIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,67 +1056,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2381</v>
+        <v>-0.2277</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2679</v>
+        <v>-0.9292</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0298</v>
+        <v>0.7015</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2484</v>
+        <v>-4.0864</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1566</v>
+        <v>-0.5496</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.405</v>
+        <v>-3.5368</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0205</v>
+        <v>-2.461</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0205</v>
+        <v>0.1395</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-2.6006</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2689</v>
+        <v>-1.6254</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1361</v>
+        <v>-0.6891</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.405</v>
+        <v>-0.9363</v>
       </c>
       <c r="P8" t="n">
-        <v>0.195</v>
+        <v>2.3398</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.195</v>
       </c>
       <c r="R8" t="n">
-        <v>0.195</v>
+        <v>2.5348</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2915</v>
+        <v>-0.3641</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2473</v>
+        <v>-0.1033</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0442</v>
+        <v>-0.2609</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.883</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.8301</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.0529</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. SUAREZ CUSTODIO</t>
+          <t>J. CHARLES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2277</v>
+        <v>-1.1541</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9292</v>
+        <v>-1.0932</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7015</v>
+        <v>-0.0608</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.0864</v>
+        <v>-0.58</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5496</v>
+        <v>0.0501</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.5368</v>
+        <v>-0.6301</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.461</v>
+        <v>-0.316</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1395</v>
+        <v>-0.3565</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.6006</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6254</v>
+        <v>-0.264</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6891</v>
+        <v>0.4066</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9363</v>
+        <v>-0.6706</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3398</v>
+        <v>-0.39</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.195</v>
+        <v>-0.9749</v>
       </c>
       <c r="R9" t="n">
-        <v>2.5348</v>
+        <v>0.585</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3641</v>
+        <v>0.4259</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1033</v>
+        <v>0.1976</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2609</v>
+        <v>0.2283</v>
       </c>
       <c r="V9" t="n">
-        <v>1.883</v>
+        <v>-0.61</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8301</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0529</v>
+        <v>-0.61</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CHARLES</t>
+          <t>A. APARICIO IZQUIERDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,58 +1222,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1541</v>
+        <v>-2.7246</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0932</v>
+        <v>-1.4591</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0608</v>
+        <v>-1.2655</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.58</v>
+        <v>-2.2314</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0501</v>
+        <v>-2.3058</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6301</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.316</v>
+        <v>-1.344</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3565</v>
+        <v>-1.279</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>-0.065</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.264</v>
+        <v>-0.8874</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4066</v>
+        <v>-1.0268</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6706</v>
+        <v>0.1394</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.39</v>
+        <v>0.585</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.585</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4259</v>
+        <v>-0.4682</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1976</v>
+        <v>-0.1151</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2283</v>
+        <v>-0.353</v>
       </c>
       <c r="V10" t="n">
         <v>-0.61</v>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. APARICIO IZQUIERDO</t>
+          <t>V. TAVERAS RAFAEL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7246</v>
+        <v>-2.7539</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4591</v>
+        <v>-3.2781</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2655</v>
+        <v>0.5242</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2314</v>
+        <v>-1.576</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3058</v>
+        <v>0.0507</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07439999999999999</v>
+        <v>-1.6266</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.344</v>
+        <v>-1.238</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.279</v>
+        <v>0.123</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.065</v>
+        <v>-1.361</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8874</v>
+        <v>-0.338</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0268</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1394</v>
+        <v>-0.2656</v>
       </c>
       <c r="P11" t="n">
-        <v>0.585</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R11" t="n">
-        <v>0.585</v>
+        <v>1.1699</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4682</v>
+        <v>-0.1194</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1151</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.353</v>
+        <v>-0.0292</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.61</v>
+        <v>-0.2786</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.61</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>V. TAVERAS RAFAEL</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,67 +1388,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7539</v>
+        <v>-3.4998</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2781</v>
+        <v>-3.3834</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5242</v>
+        <v>-0.1164</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.576</v>
+        <v>-3.4455</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0507</v>
+        <v>-0.6783</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6266</v>
+        <v>-2.7673</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.238</v>
+        <v>-2.4975</v>
       </c>
       <c r="K12" t="n">
-        <v>0.123</v>
+        <v>-0.537</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.361</v>
+        <v>-1.9605</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.338</v>
+        <v>-0.948</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.1413</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2656</v>
+        <v>-0.8067</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.7799</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9499</v>
+        <v>-0.9749</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1699</v>
+        <v>0.9749</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1194</v>
+        <v>-0.0543</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.09030000000000001</v>
+        <v>0.089</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0292</v>
+        <v>-0.1433</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.2786</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2786</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1471,157 +1471,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4998</v>
+        <v>11.3758</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3834</v>
+        <v>9.2682</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1164</v>
+        <v>2.1077</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.4455</v>
+        <v>-2.0165</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6783</v>
+        <v>2.7307</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.7673</v>
+        <v>-4.7471</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.4975</v>
+        <v>8.8088</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.537</v>
+        <v>6.882400000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.9605</v>
+        <v>1.926299999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.948</v>
+        <v>-10.8253</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1413</v>
+        <v>-4.152</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8067</v>
+        <v>-6.6732</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>3.8997</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9749</v>
+        <v>-12.674</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9749</v>
+        <v>16.5738</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0543</v>
+        <v>3.1274</v>
       </c>
       <c r="T13" t="n">
-        <v>0.089</v>
+        <v>3.252699999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1433</v>
+        <v>-0.1253</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.3649</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>9.880400000000002</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>play_by_play_2536121_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-3.5154</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>MOVISTAR ESTUDIANTES</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.3757</v>
+        <v>7.1515</v>
       </c>
       <c r="E14" t="n">
-        <v>9.2682</v>
+        <v>6.6611</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1077</v>
+        <v>0.4904</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.0165</v>
+        <v>6.2355</v>
       </c>
       <c r="H14" t="n">
-        <v>2.730599999999999</v>
+        <v>0.643</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.7471</v>
+        <v>5.5925</v>
       </c>
       <c r="J14" t="n">
-        <v>8.8088</v>
+        <v>7.861</v>
       </c>
       <c r="K14" t="n">
-        <v>6.882399999999999</v>
+        <v>1.6077</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9263</v>
+        <v>6.2532</v>
       </c>
       <c r="M14" t="n">
-        <v>-10.8253</v>
+        <v>-1.6255</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.152</v>
+        <v>-0.9648</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.6732</v>
+        <v>-0.6607</v>
       </c>
       <c r="P14" t="n">
-        <v>3.8997</v>
+        <v>1.1699</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.674</v>
+        <v>-1.1699</v>
       </c>
       <c r="R14" t="n">
-        <v>16.5738</v>
+        <v>2.3398</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1274</v>
+        <v>-0.2539</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2527</v>
+        <v>-0.0299</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1253</v>
+        <v>-0.2239</v>
       </c>
       <c r="V14" t="n">
-        <v>6.3649</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>9.8804</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.5154</v>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2536121_LIGAREGULARA_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>J. SCHILB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,67 +1633,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.1515</v>
+        <v>4.1446</v>
       </c>
       <c r="E15" t="n">
-        <v>6.6611</v>
+        <v>5.8255</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4904</v>
+        <v>-1.6809</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2355</v>
+        <v>4.5625</v>
       </c>
       <c r="H15" t="n">
-        <v>0.643</v>
+        <v>2.2944</v>
       </c>
       <c r="I15" t="n">
-        <v>5.5925</v>
+        <v>2.2681</v>
       </c>
       <c r="J15" t="n">
-        <v>7.861</v>
+        <v>5.1024</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6077</v>
+        <v>2.5753</v>
       </c>
       <c r="L15" t="n">
-        <v>6.2532</v>
+        <v>2.5271</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6255</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9648</v>
+        <v>-0.2808</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6607</v>
+        <v>-0.259</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1699</v>
+        <v>-0.195</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1699</v>
+        <v>-1.9499</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3398</v>
+        <v>1.7549</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2539</v>
+        <v>0.3871</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0299</v>
+        <v>0.8429</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2239</v>
+        <v>-0.4558</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.8301</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.4401</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SCHILB</t>
+          <t>G. DE BONROSTRO GALLEGO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1446</v>
+        <v>1.2551</v>
       </c>
       <c r="E16" t="n">
-        <v>5.8255</v>
+        <v>1.7788</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6809</v>
+        <v>-0.5238</v>
       </c>
       <c r="G16" t="n">
-        <v>4.5625</v>
+        <v>0.3629</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2944</v>
+        <v>-0.3223</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2681</v>
+        <v>0.6852</v>
       </c>
       <c r="J16" t="n">
-        <v>5.1024</v>
+        <v>1.2436</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5753</v>
+        <v>0.0205</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5271</v>
+        <v>1.2231</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.8807</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2808</v>
+        <v>-0.3428</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.259</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.195</v>
+        <v>0.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9499</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7549</v>
+        <v>0.39</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3871</v>
+        <v>-0.3864</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8429</v>
+        <v>-0.3533</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4558</v>
+        <v>-0.0331</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.61</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8301</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.4401</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. DE BONROSTRO GALLEGO</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2551</v>
+        <v>0.9336</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7788</v>
+        <v>0.8376</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5238</v>
+        <v>0.096</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3629</v>
+        <v>0.2263</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3223</v>
+        <v>0.5</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6852</v>
+        <v>-0.2736</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2436</v>
+        <v>0.9006</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0205</v>
+        <v>0.7791</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2231</v>
+        <v>0.1215</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8807</v>
+        <v>-0.6742</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3428</v>
+        <v>-0.2791</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.3951</v>
       </c>
       <c r="P17" t="n">
-        <v>0.39</v>
+        <v>0.585</v>
       </c>
       <c r="Q17" t="n">
+        <v>-0.195</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.7799</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.1223</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.1465</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="V17" t="n">
         <v>0</v>
       </c>
-      <c r="R17" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="S17" t="n">
-        <v>-0.3864</v>
-      </c>
-      <c r="T17" t="n">
-        <v>-0.3533</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-0.0331</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.8885999999999999</v>
-      </c>
       <c r="W17" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.2786</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>S. GRADIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9336</v>
+        <v>-0.9445</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8376</v>
+        <v>0.854</v>
       </c>
       <c r="F18" t="n">
-        <v>0.096</v>
+        <v>-1.7985</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2263</v>
+        <v>0.0779</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2736</v>
+        <v>-0.5929</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9006</v>
+        <v>0.6881</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7791</v>
+        <v>1.2876</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1215</v>
+        <v>-0.5995</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6742</v>
+        <v>-0.6102</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2791</v>
+        <v>-0.6168</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3951</v>
+        <v>0.0066</v>
       </c>
       <c r="P18" t="n">
-        <v>0.585</v>
+        <v>-0.195</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.195</v>
+        <v>-0.9749</v>
       </c>
       <c r="R18" t="n">
         <v>0.7799</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1223</v>
+        <v>0.3926</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1465</v>
+        <v>0.5837</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2688</v>
+        <v>-0.1911</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2786</v>
+        <v>0.5571</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2786</v>
+        <v>-1.7772</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. GRADIN</t>
+          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9445</v>
+        <v>-1.3972</v>
       </c>
       <c r="E19" t="n">
-        <v>0.854</v>
+        <v>-0.9123</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7985</v>
+        <v>-0.4849</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0779</v>
+        <v>-0.8314</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6709000000000001</v>
+        <v>-0.9562</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5929</v>
+        <v>0.1248</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6881</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2876</v>
+        <v>-0.6805</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5995</v>
+        <v>0.1215</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6102</v>
+        <v>-0.2724</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6168</v>
+        <v>-0.2756</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0066</v>
+        <v>0.0033</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.195</v>
+        <v>0.585</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7799</v>
+        <v>0.585</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3926</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5837</v>
+        <v>-0.3533</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1911</v>
+        <v>-0.1875</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2201</v>
+        <v>-0.61</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5571</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7772</v>
+        <v>-0.61</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3972</v>
+        <v>-1.89</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9123</v>
+        <v>0.1953</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4849</v>
+        <v>-2.0853</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8314</v>
+        <v>0.1209</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9562</v>
+        <v>0.0672</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1248</v>
+        <v>0.0537</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5590000000000001</v>
+        <v>1.4101</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6805</v>
+        <v>1.3696</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1215</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2724</v>
+        <v>-1.2893</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2756</v>
+        <v>-1.3024</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0033</v>
+        <v>0.0132</v>
       </c>
       <c r="P20" t="n">
-        <v>0.585</v>
+        <v>-0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1699</v>
       </c>
       <c r="R20" t="n">
-        <v>0.585</v>
+        <v>1.1699</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.1279</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3533</v>
+        <v>0.008</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1875</v>
+        <v>-0.1359</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.61</v>
+        <v>-1.883</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.0529</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.61</v>
+        <v>-1.8301</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.89</v>
+        <v>-3.1871</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1953</v>
+        <v>-3.5539</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0853</v>
+        <v>0.3668</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1209</v>
+        <v>-1.0111</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0672</v>
+        <v>-1.8098</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0537</v>
+        <v>0.7987</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4101</v>
+        <v>0.078</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3696</v>
+        <v>-0.578</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0405</v>
+        <v>0.656</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2893</v>
+        <v>-1.0891</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3024</v>
+        <v>-1.2318</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0132</v>
+        <v>0.1427</v>
       </c>
       <c r="P21" t="n">
-        <v>-0</v>
+        <v>-1.9499</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1699</v>
+        <v>-3.1198</v>
       </c>
       <c r="R21" t="n">
         <v>1.1699</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1279</v>
+        <v>0.0524</v>
       </c>
       <c r="T21" t="n">
-        <v>0.008</v>
+        <v>-0.4592</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1359</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.883</v>
+        <v>-0.2786</v>
       </c>
       <c r="W21" t="n">
         <v>-0.0529</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8301</v>
+        <v>-0.2256</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>D. DAMIAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1871</v>
+        <v>-3.4794</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5539</v>
+        <v>-3.1297</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3668</v>
+        <v>-0.3498</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0111</v>
+        <v>-0.6091</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.8098</v>
+        <v>-0.619</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7987</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>0.078</v>
+        <v>-0.4809</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.578</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.656</v>
+        <v>0.1295</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0891</v>
+        <v>-0.1282</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2318</v>
+        <v>-0.0086</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1427</v>
+        <v>-0.1196</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9499</v>
+        <v>-1.3649</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1198</v>
+        <v>-2.9248</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1699</v>
+        <v>1.5599</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0524</v>
+        <v>0.4305</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4592</v>
+        <v>0.7133</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5116000000000001</v>
+        <v>-0.2828</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2786</v>
+        <v>-1.9359</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.0529</v>
+        <v>-0.4373</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2256</v>
+        <v>-1.4986</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. DAMIAN</t>
+          <t>H. APARICIO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4794</v>
+        <v>-4.8217</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1297</v>
+        <v>-3.5066</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3498</v>
+        <v>-1.315</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6091</v>
+        <v>-1.3243</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.619</v>
+        <v>-0.5143</v>
       </c>
       <c r="I23" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4809</v>
+        <v>-0.578</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6104000000000001</v>
+        <v>0.1025</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1295</v>
+        <v>-0.6805</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1282</v>
+        <v>-0.7463</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0086</v>
+        <v>-0.6168</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1196</v>
+        <v>-0.1295</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3649</v>
+        <v>-2.5348</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.9248</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5599</v>
+        <v>0.39</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4305</v>
+        <v>0.2575</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7133</v>
+        <v>-0.0039</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2828</v>
+        <v>0.2614</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.9359</v>
+        <v>-1.2201</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.4373</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4986</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H. APARICIO RODRIGUEZ</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,67 +2380,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8217</v>
+        <v>-6.5101</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.5066</v>
+        <v>-7.1576</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.315</v>
+        <v>0.6475</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3243</v>
+        <v>-5.7937</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5143</v>
+        <v>-2.6845</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.1092</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.578</v>
+        <v>-4.8405</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1025</v>
+        <v>-1.7215</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6805</v>
+        <v>-3.1191</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7463</v>
+        <v>-0.9532</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6168</v>
+        <v>-0.963</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1295</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.5348</v>
+        <v>-0.39</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9248</v>
+        <v>-2.1448</v>
       </c>
       <c r="R24" t="n">
-        <v>0.39</v>
+        <v>1.7549</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2575</v>
+        <v>-0.8306</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0039</v>
+        <v>-0.6764</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2614</v>
+        <v>-0.1542</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2201</v>
+        <v>0.5042</v>
       </c>
       <c r="W24" t="n">
+        <v>0.5042</v>
+      </c>
+      <c r="X24" t="n">
         <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>-1.2201</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,152 +2463,69 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.5101</v>
+        <v>-8.745200000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.1576</v>
+        <v>-2.107800000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6475</v>
+        <v>-6.6375</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.7937</v>
+        <v>2.016399999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.6845</v>
+        <v>-2.7306</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.1092</v>
+        <v>4.747199999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.8405</v>
+        <v>10.8254</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.7215</v>
+        <v>4.151899999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.1191</v>
+        <v>6.673300000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9532</v>
+        <v>-8.8089</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.963</v>
+        <v>-6.882500000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>0.009900000000000001</v>
+        <v>-1.926</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.39</v>
+        <v>-3.899700000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.1448</v>
+        <v>-16.5738</v>
       </c>
       <c r="R25" t="n">
-        <v>1.7549</v>
+        <v>12.6741</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8306</v>
+        <v>-0.4972</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6764</v>
+        <v>0.1254</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1542</v>
+        <v>-0.6224999999999998</v>
       </c>
       <c r="V25" t="n">
-        <v>0.5042</v>
+        <v>-6.3649</v>
       </c>
       <c r="W25" t="n">
-        <v>0.5042</v>
+        <v>3.5155</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536121_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>MOVISTAR ESTUDIANTES</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-8.745200000000001</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-2.107800000000001</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-6.6375</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2.016399999999999</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-2.7306</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4.747199999999999</v>
-      </c>
-      <c r="J26" t="n">
-        <v>10.8254</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.151899999999999</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6.673300000000001</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-8.8089</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-6.882500000000001</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-1.926</v>
-      </c>
-      <c r="P26" t="n">
-        <v>-3.899700000000001</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-16.5738</v>
-      </c>
-      <c r="R26" t="n">
-        <v>12.6741</v>
-      </c>
-      <c r="S26" t="n">
-        <v>-0.4972</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.1254</v>
-      </c>
-      <c r="U26" t="n">
-        <v>-0.6224999999999998</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-6.3649</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3.5155</v>
-      </c>
-      <c r="X26" t="n">
         <v>-9.8803</v>
       </c>
-      <c r="Y26" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
